--- a/04_DESIGN_TABLES/DesignTable_4603.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_4603.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2585,24 +2590,55 @@
           <t>4603-16-16-NWO-FG</t>
         </is>
       </c>
+      <c r="B36" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>4603-16-16-NWO-FG</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4603-16-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4603-16-16 NWO (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4603-16-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4603-16-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.844 not modelled: Q-HOSEB-BORE (a) = one bore 0.844 (D@BORE) through both legs</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2613,6 +2649,11 @@
       <c r="P36" t="inlineStr">
         <is>
           <t>4603-16-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
